--- a/data/神火股份_000933.SZ抓取数据.xlsx
+++ b/data/神火股份_000933.SZ抓取数据.xlsx
@@ -284,7 +284,7 @@
         <v>41.77</v>
       </c>
       <c r="G3" s="4">
-        <v>7.98</v>
+        <v>8.7</v>
       </c>
       <c r="H3" s="4">
         <v>2.16</v>
